--- a/bench.xlsx
+++ b/bench.xlsx
@@ -46,7 +46,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="1" xr:uid="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}">
+    <comment ref="E13" authorId="1" xr:uid="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}">
       <text>
         <r>
           <rPr>
@@ -117,12 +117,12 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={CA9AA1C9-6AD3-364A-9DC1-052A22FDB9B4}</author>
-    <author>tc={BDC83CEB-A7B1-AC8D-239A-6FEB488AC23E}</author>
-    <author>tc={10C544B4-EB2D-391F-CA6A-D49CF56E7AE9}</author>
+    <author>tc={FBA8A04F-1144-D4CE-3955-9139357F1DF7}</author>
+    <author>tc={49BA0359-1DD6-6E69-0623-10EC65534207}</author>
+    <author>tc={71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" xr:uid="{CA9AA1C9-6AD3-364A-9DC1-052A22FDB9B4}">
+    <comment ref="A2" authorId="0" xr:uid="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="1" xr:uid="{BDC83CEB-A7B1-AC8D-239A-6FEB488AC23E}">
+    <comment ref="A3" authorId="1" xr:uid="{49BA0359-1DD6-6E69-0623-10EC65534207}">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="2" xr:uid="{10C544B4-EB2D-391F-CA6A-D49CF56E7AE9}">
+    <comment ref="A4" authorId="2" xr:uid="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>stylegan3-r</t>
   </si>
@@ -204,25 +204,34 @@
     <t xml:space="preserve">&lt; source</t>
   </si>
   <si>
-    <t xml:space="preserve">A770 (XPU)</t>
+    <t xml:space="preserve">A770 (XPU, PyTorch 2.1.x)</t>
   </si>
   <si>
     <t xml:space="preserve">bench log 2024-12-03.html</t>
   </si>
   <si>
-    <t xml:space="preserve">PVC Max 1100 (XPU)</t>
+    <t xml:space="preserve">PVC Max 1100 (XPU, PyTorch 2.1.x)</t>
   </si>
   <si>
     <t xml:space="preserve">Intel PVC VM stylegan3 more speed measurements (before+after the 5x speedup commit and -01 vs -O3) 2024-11-21.txt</t>
   </si>
   <si>
-    <t xml:space="preserve">1080Ti (CUDA)</t>
+    <t xml:space="preserve">1080Ti (CUDA, PyTorch 1.9.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">A770 ("ref")</t>
+    <t xml:space="preserve">1080Ti (CUDA, PyTorch 2.1.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bench log 2024-12-04.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A770 ("ref", PyTorch 2.1.x)</t>
   </si>
   <si>
     <t xml:space="preserve">1080Ti ("ref", PyTorch 1.9.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1080Ti ("ref", PyTorch 2.1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">Notes: measured with "./bench3.sh" (gen_video.py with [network_variant]-afhqv2-512x512.pkl), always using the median value as the result</t>
@@ -246,7 +255,7 @@
     <t>2.1.40+xpu</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9.1 (py3.9_cuda11.1_cudnn8.0.5_0)</t>
+    <t xml:space="preserve">1.9.1 (py3.9_cuda11.1_cudnn8.0.5_0), and later re-measured with 2.1.2 (py3.9_cuda12.1_cudnn8.9.2_0)</t>
   </si>
   <si>
     <t>driver</t>
@@ -268,6 +277,9 @@
   </si>
   <si>
     <t xml:space="preserve">CUDA Version: 12.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1080Ti (CUDA)</t>
   </si>
 </sst>
 </file>
@@ -418,7 +430,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>A770 (XPU)</c:v>
+                  <c:v>A770 (XPU, PyTorch 2.1.x)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -517,7 +529,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>PVC Max 1100 (XPU)</c:v>
+                  <c:v>PVC Max 1100 (XPU, PyTorch 2.1.x)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -616,7 +628,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1080Ti (CUDA)</c:v>
+                  <c:v>1080Ti (CUDA, PyTorch 1.9.1)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -715,7 +727,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>A770 ("ref")</c:v>
+                  <c:v>1080Ti (CUDA, PyTorch 2.1.2)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -793,13 +805,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1.01</c:v>
+                  <c:v>13.86</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.77</c:v>
+                  <c:v>7.04</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24.52</c:v>
+                  <c:v>36.68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -814,7 +826,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1080Ti ("ref")</c:v>
+                  <c:v>A770 ("ref", PyTorch 2.1.x)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -892,6 +904,105 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.77</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti ("ref", PyTorch 1.9.1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:dLblPos val="outEnd"/>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="1"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:txPr>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$7:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
                   <c:v>0.24</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -899,6 +1010,107 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>15.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti ("ref", PyTorch 2.1.2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:dLblPos val="outEnd"/>
+            <c:separator xml:space="preserve"> </c:separator>
+            <c:showBubbleSize val="0"/>
+            <c:showCatName val="0"/>
+            <c:showLegendKey val="0"/>
+            <c:showPercent val="0"/>
+            <c:showSerName val="0"/>
+            <c:showVal val="1"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr/>
+              </a:p>
+            </c:txPr>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$8:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -944,11 +1156,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-26"/>
-        <c:axId val="2140841633"/>
-        <c:axId val="2140841634"/>
+        <c:axId val="2140841721"/>
+        <c:axId val="2140841722"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2140841633"/>
+        <c:axId val="2140841721"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -992,7 +1204,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2140841634"/>
+        <c:crossAx val="2140841722"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1001,7 +1213,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2140841634"/>
+        <c:axId val="2140841722"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1027,7 +1239,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" vert="horz"/>
               <a:p>
                 <a:pPr>
                   <a:defRPr/>
@@ -1043,7 +1255,7 @@
           <c:layout/>
           <c:overlay val="0"/>
           <c:txPr>
-            <a:bodyPr/>
+            <a:bodyPr rot="0" vert="horz"/>
             <a:p>
               <a:pPr>
                 <a:defRPr/>
@@ -1084,7 +1296,7 @@
             <a:endParaRPr/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2140841633"/>
+        <c:crossAx val="2140841721"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1139,8 +1351,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="4895849" y="314324"/>
-      <a:ext cx="6686549" cy="3681412"/>
+      <a:off x="6257924" y="1133474"/>
+      <a:ext cx="8124824" cy="4119562"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -3009,27 +3221,27 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>361949</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>138112</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>342899</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="197694986" name=""/>
+        <xdr:cNvPr id="370919270" name=""/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="4895849" y="314324"/>
-        <a:ext cx="6686549" cy="3681412"/>
+        <a:off x="6257924" y="1133474"/>
+        <a:ext cx="8124824" cy="4119562"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3081,7 +3293,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="user" id="{AFCEB222-9418-A19C-68A0-D60362A1939D}" userId="user" providerId="Teamlab"/>
+  <person displayName="user" id="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" userId="user" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -3577,20 +3789,20 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="E12" dT="2024-12-03T17:44:41.53Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="0">
+  <threadedComment ref="E13" dT="2024-12-03T17:44:41.53Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
     <text xml:space="preserve">TODO try upgrading and re-measuring
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 on a VM instance on Intel Tiber Developer Cloud
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -3599,15 +3811,15 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{CA9AA1C9-6AD3-364A-9DC1-052A22FDB9B4}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{BDC83CEB-A7B1-AC8D-239A-6FEB488AC23E}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{AFCEB222-9418-A19C-68A0-D60362A1939D}" id="{10C544B4-EB2D-391F-CA6A-D49CF56E7AE9}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -3692,97 +3904,130 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
-        <v>1.01</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1.77</v>
-      </c>
-      <c r="D5" s="3">
-        <v>24.52</v>
+      <c r="B5" s="2">
+        <v>13.859999999999999</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7.04</v>
+      </c>
+      <c r="D5" s="2">
+        <v>36.68</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="C6">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="D6">
-        <v>15.130000000000001</v>
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.01</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.77</v>
+      </c>
+      <c r="D6" s="2">
+        <v>24.52</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="14.25"/>
-    <row r="8" ht="14.25"/>
-    <row r="9" ht="14.25">
-      <c r="A9" t="s">
-        <v>11</v>
+    <row r="7" ht="14.25">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.92000000000000004</v>
+      </c>
+      <c r="D7">
+        <v>15.130000000000001</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="B8">
+        <v>0.23000000000000001</v>
+      </c>
+      <c r="C8">
+        <v>0.81999999999999995</v>
+      </c>
+      <c r="D8">
+        <v>22.699999999999999</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="11" ht="14.25"/>
     <row r="12" ht="14.25">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>17</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13" ht="14.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
         <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>23</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>24</v>
       </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +4061,7 @@
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>7.4500000000000002</v>
@@ -3830,7 +4075,7 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>6.4199999999999999</v>
@@ -3844,7 +4089,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>11.9</v>
@@ -3858,7 +4103,7 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/bench.xlsx
+++ b/bench.xlsx
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>stylegan3-r</t>
   </si>
@@ -279,6 +279,21 @@
     <t xml:space="preserve">CUDA Version: 12.2</t>
   </si>
   <si>
+    <t xml:space="preserve">1080Ti (speedup "ref" -&gt; CUDA, PyTorch 1.9.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1080Ti (speedup "ref" -&gt; CUDA, PyTorch 2.1.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A770 (speedup "ref" -&gt; XPU, PyTorch 2.1.x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"ref" speedup A770 vs 1080Ti (PyTorch 2.1.x vs 1.9.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"ref" speedup A770 vs 1080Ti (PyTorch 2.1.x vs 2.1.2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1080Ti (CUDA)</t>
   </si>
 </sst>
@@ -325,7 +340,9 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,6 +468,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -550,6 +568,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -649,6 +668,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -748,6 +768,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -847,6 +868,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -946,6 +968,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -1047,6 +1070,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -1121,6 +1145,7 @@
           <c:separator xml:space="preserve"> </c:separator>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
@@ -1351,7 +1376,7 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="6257924" y="1133474"/>
+      <a:off x="6257923" y="1133474"/>
       <a:ext cx="8124824" cy="4119562"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
@@ -1513,6 +1538,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -1613,6 +1639,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -1713,6 +1740,7 @@
             <c:separator xml:space="preserve"> </c:separator>
             <c:showBubbleSize val="0"/>
             <c:showCatName val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:showLegendKey val="0"/>
             <c:showPercent val="0"/>
             <c:showSerName val="0"/>
@@ -1787,6 +1815,7 @@
           <c:separator xml:space="preserve"> </c:separator>
           <c:showBubbleSize val="0"/>
           <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
           <c:showPercent val="0"/>
           <c:showSerName val="0"/>
@@ -3222,7 +3251,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>371474</xdr:colOff>
+      <xdr:colOff>371473</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
@@ -3240,7 +3269,7 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="6257924" y="1133474"/>
+        <a:off x="6257923" y="1133474"/>
         <a:ext cx="8124824" cy="4119562"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3261,7 +3290,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>114299</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>66673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
@@ -3293,7 +3322,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="user" id="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" userId="user" providerId="Teamlab"/>
+  <person displayName="user" id="{D8426B48-3D18-4E14-7890-79335D173E8D}" userId="user" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -3789,20 +3818,20 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="E13" dT="2024-12-03T17:44:41.53Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
+  <threadedComment ref="E13" dT="2024-12-03T17:44:41.53Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
     <text xml:space="preserve">TODO try upgrading and re-measuring
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 on a VM instance on Intel Tiber Developer Cloud
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -3811,15 +3840,15 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{2273A713-94E1-773E-E6FE-AFA954FF6CEB}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -3830,7 +3859,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.28125"/>
+    <col customWidth="1" min="1" max="1" width="32.28125"/>
     <col customWidth="1" min="2" max="3" width="12.140625"/>
     <col customWidth="1" min="4" max="4" width="14.140625"/>
   </cols>
@@ -3918,7 +3947,7 @@
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2">
@@ -3935,7 +3964,7 @@
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7">
@@ -3995,7 +4024,7 @@
       <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
@@ -4026,8 +4055,53 @@
       <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22">
+        <f>C4/C7</f>
+        <v>11.163043478260869</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <f>C5/C8</f>
+        <v>8.5853658536585371</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24">
+        <f>C2/C6</f>
+        <v>5.6553672316384178</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27">
+        <f>C6/C7</f>
+        <v>1.9239130434782608</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28">
+        <f>C6/C8</f>
+        <v>2.1585365853658538</v>
       </c>
     </row>
   </sheetData>
@@ -4089,7 +4163,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>11.9</v>

--- a/bench.xlsx
+++ b/bench.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="current" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="backup" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="stddev of metrics" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="backup" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -20,9 +21,13 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={5D1DD697-3B31-24C3-D1FC-4F10BC94625B}</author>
+    <author>tc={1CB70762-CB98-18A3-8B23-8B0C43552DB3}</author>
     <author>tc={44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}</author>
+    <author>tc={D60FF92D-CD85-77A7-BAF7-B50E5A8F386D}</author>
+    <author>tc={0A840647-343D-ECD8-EE73-9B5128B511C0}</author>
     <author>tc={9885B1C3-AB22-94B7-30B7-E8A667F23725}</author>
     <author>tc={07C5CB9B-011A-F201-BE01-B6ED5DCC747A}</author>
+    <author>tc={3D18DD77-473E-3CE6-83E6-86E80A773716}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" xr:uid="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}">
@@ -42,11 +47,34 @@
           </rPr>
           <t xml:space="preserve">
 heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
+exact pytorch version: 2.1.0.post3+cxx11.abi
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="1" xr:uid="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}">
+    <comment ref="A12" authorId="1" xr:uid="{1CB70762-CB98-18A3-8B23-8B0C43552DB3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+heads/debug_profiling-0-gb9cee85 with "stylegan" environment
+re-measure with current commit
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="2" xr:uid="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}">
       <text>
         <r>
           <rPr>
@@ -67,7 +95,51 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="2" xr:uid="{9885B1C3-AB22-94B7-30B7-E8A667F23725}">
+    <comment ref="A3" authorId="3" xr:uid="{D60FF92D-CD85-77A7-BAF7-B50E5A8F386D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_1_40_xpu"
+re-measured current commit, with current GPU driver
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="4" xr:uid="{0A840647-343D-ECD8-EE73-9B5128B511C0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_3_110_xpu"
+torch 2.3.1+cxx11.abi
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="5" xr:uid="{9885B1C3-AB22-94B7-30B7-E8A667F23725}">
       <text>
         <r>
           <rPr>
@@ -89,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="3" xr:uid="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}">
+    <comment ref="A6" authorId="6" xr:uid="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}">
       <text>
         <r>
           <rPr>
@@ -106,6 +178,27 @@
           </rPr>
           <t xml:space="preserve">
 heads/debug_profiling-0-g9390a36 with "stylegan" environment
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="7" xr:uid="{3D18DD77-473E-3CE6-83E6-86E80A773716}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+heads/debug_profiling-0-gb9cee85 with "stylegan" environment
 </t>
         </r>
       </text>
@@ -190,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>stylegan3-r</t>
   </si>
@@ -210,6 +303,15 @@
     <t xml:space="preserve">bench log 2024-12-03.html</t>
   </si>
   <si>
+    <t xml:space="preserve">runs.log, 2025-03-27T15:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A770 (XPU, PyTorch 2.3.x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">runs.log, 2025-03-28T17:10-11</t>
+  </si>
+  <si>
     <t xml:space="preserve">PVC Max 1100 (XPU, PyTorch 2.1.x)</t>
   </si>
   <si>
@@ -219,6 +321,9 @@
     <t xml:space="preserve">1080Ti (CUDA, PyTorch 1.9.1)</t>
   </si>
   <si>
+    <t xml:space="preserve">runs.log, 2025-03-28T17:35-36</t>
+  </si>
+  <si>
     <t xml:space="preserve">1080Ti (CUDA, PyTorch 2.1.2)</t>
   </si>
   <si>
@@ -228,9 +333,18 @@
     <t xml:space="preserve">A770 ("ref", PyTorch 2.1.x)</t>
   </si>
   <si>
+    <t xml:space="preserve">A770 ("ref", PyTorch 2.3.x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">runs.log, 2025-03-27T17:45-48</t>
+  </si>
+  <si>
     <t xml:space="preserve">1080Ti ("ref", PyTorch 1.9.1)</t>
   </si>
   <si>
+    <t xml:space="preserve">runs.log, 2025-03-27T17:38-44</t>
+  </si>
+  <si>
     <t xml:space="preserve">1080Ti ("ref", PyTorch 2.1.2)</t>
   </si>
   <si>
@@ -252,6 +366,9 @@
     <t>pytorch</t>
   </si>
   <si>
+    <t xml:space="preserve">2.1.40+xpu, then 2.3.110+xpu</t>
+  </si>
+  <si>
     <t>2.1.40+xpu</t>
   </si>
   <si>
@@ -261,7 +378,7 @@
     <t>driver</t>
   </si>
   <si>
-    <t xml:space="preserve">intel-i915-dkms: 1.24.3.23.240419.26+i30-1</t>
+    <t xml:space="preserve">intel-i915-dkms 1.24.3.23.240419.26+i30-1, then intel-i915-dkms 1.24.6.12.240823.13+i14-1</t>
   </si>
   <si>
     <t>?</t>
@@ -273,12 +390,15 @@
     <t xml:space="preserve">level zero</t>
   </si>
   <si>
-    <t xml:space="preserve">intel-level-zero-gpu: 1.3.29735.27-914~22.04</t>
+    <t xml:space="preserve">intel-level-zero-gpu 1.3.29735.27-914~22.04, then libze-intel-gpu1 24.39.31294.20-1032~22.04</t>
   </si>
   <si>
     <t xml:space="preserve">CUDA Version: 12.2</t>
   </si>
   <si>
+    <t xml:space="preserve">comparing matching PyTorh versions (major.minor):</t>
+  </si>
+  <si>
     <t xml:space="preserve">1080Ti (speedup "ref" -&gt; CUDA, PyTorch 1.9.1)</t>
   </si>
   <si>
@@ -288,10 +408,91 @@
     <t xml:space="preserve">A770 (speedup "ref" -&gt; XPU, PyTorch 2.1.x)</t>
   </si>
   <si>
+    <t xml:space="preserve">A770 (speedup "ref" -&gt; XPU, PyTorch 2.3.x)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;- PT/IPEX 2.3 is slower than 2.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">"ref" speedup A770 vs 1080Ti (PyTorch 2.1.x vs 1.9.1)</t>
   </si>
   <si>
     <t xml:space="preserve">"ref" speedup A770 vs 1080Ti (PyTorch 2.1.x vs 2.1.2)</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>2025-03-27T15:36:46+01:00</t>
+  </si>
+  <si>
+    <t>Z790P</t>
+  </si>
+  <si>
+    <t>stylegan3_2_3_110_xpu</t>
+  </si>
+  <si>
+    <t>heads/debug_profiling-0-gdab3304-dirty</t>
+  </si>
+  <si>
+    <t>stylegan2-afhqv2-512x512.pkl</t>
+  </si>
+  <si>
+    <t>min/mean/median/max</t>
+  </si>
+  <si>
+    <t>rate:</t>
+  </si>
+  <si>
+    <t>it/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inter-run standard deviation (percentage of average value)</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:11:15+01:00</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:14:01+01:00</t>
+  </si>
+  <si>
+    <t>2025-03-27T15:33:32+01:00</t>
+  </si>
+  <si>
+    <t>stylegan3-r-afhqv2-512x512.pkl</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:10:37+01:00</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:13:23+01:00</t>
+  </si>
+  <si>
+    <t>2025-03-27T15:36:29+01:00</t>
+  </si>
+  <si>
+    <t>stylegan3-t-afhqv2-512x512.pkl</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:10:57+01:00</t>
+  </si>
+  <si>
+    <t>2025-03-27T17:13:43+01:00</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-&gt; we should probably measure the average it/s or max it/s rather than the currently used median speed</t>
   </si>
   <si>
     <t xml:space="preserve">1080Ti (CUDA)</t>
@@ -335,13 +536,21 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,7 +641,15 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
-        <c:manualLayout/>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.074540"/>
+          <c:y val="0.120810"/>
+          <c:w val="0.911380"/>
+          <c:h val="0.729310"/>
+        </c:manualLayout>
       </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
@@ -543,7 +760,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$3</c:f>
+              <c:f>current!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -621,7 +838,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$3:$D$3</c:f>
+              <c:f>current!$B$5:$D$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -643,7 +860,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$4</c:f>
+              <c:f>current!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -721,7 +938,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$4:$D$4</c:f>
+              <c:f>current!$B$6:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -743,7 +960,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$5</c:f>
+              <c:f>current!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -821,7 +1038,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$5:$D$5</c:f>
+              <c:f>current!$B$8:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -843,7 +1060,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$6</c:f>
+              <c:f>current!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -921,7 +1138,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$6:$D$6</c:f>
+              <c:f>current!$B$9:$D$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -943,7 +1160,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$7</c:f>
+              <c:f>current!$A$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1021,7 +1238,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$7:$D$7</c:f>
+              <c:f>current!$B$12:$D$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1043,7 +1260,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>current!$A$8</c:f>
+              <c:f>current!$A$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1123,7 +1340,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>current!$B$8:$D$8</c:f>
+              <c:f>current!$B$14:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1376,8 +1593,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="6257923" y="1133474"/>
-      <a:ext cx="8124824" cy="4119562"/>
+      <a:off x="7524747" y="1885947"/>
+      <a:ext cx="8124824" cy="4591049"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -1420,6 +1637,1016 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A770 (XPU, PyTorch 2.1.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$2:$D$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7.45</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A770 (XPU, PyTorch 2.1.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$3:$D$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>27.23</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A770 (XPU, PyTorch 2.3.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$4:$D$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6.83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.29</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PVC Max 1100 (XPU, PyTorch 2.1.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$5:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6.42</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.91</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti (CUDA, PyTorch 1.9.1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$6:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.83</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti (CUDA, PyTorch 1.9.1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$7:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>12.63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.07</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti (CUDA, PyTorch 2.1.2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$8:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>13.86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.68</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A770 ("ref", PyTorch 2.1.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$9:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.77</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A770 ("ref", PyTorch 2.3.x)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$11:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.69</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti ("ref", PyTorch 1.9.1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$12:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti ("ref", PyTorch 1.9.1)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$13:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>current!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1080Ti ("ref", PyTorch 2.1.2)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>current!$B$1:$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>stylegan3-r</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stylegan3-t</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>stylegan2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>current!$B$14:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-26"/>
+        <c:axId val="2140841805"/>
+        <c:axId val="2140841806"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2140841805"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841806"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2140841806"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr bwMode="auto">
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2140841805"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0" flipH="0" flipV="0">
+      <a:off x="5895974" y="4090985"/>
+      <a:ext cx="4552949" cy="2905124"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2188,6 +3415,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3246,20 +4513,549 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>371473</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:colOff>371472</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76197</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:colOff>571497</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>142872</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3269,12 +5065,44 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="6257923" y="1133474"/>
-        <a:ext cx="8124824" cy="4119562"/>
+        <a:off x="7524747" y="1885947"/>
+        <a:ext cx="8124824" cy="4591049"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>109535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>119060</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1017282525" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="0" flipH="0" flipV="0">
+        <a:off x="5895974" y="4090985"/>
+        <a:ext cx="4552949" cy="2905124"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3322,7 +5150,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="user" id="{D8426B48-3D18-4E14-7890-79335D173E8D}" userId="user" providerId="Teamlab"/>
+  <person displayName="user" id="{296568FF-0662-2C9F-C581-89AAD6A06E95}" userId="user" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -3818,21 +5646,41 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
+exact pytorch version: 2.1.0.post3+cxx11.abi
 </text>
   </threadedComment>
-  <threadedComment ref="E13" dT="2024-12-03T17:44:41.53Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
+  <threadedComment ref="A12" dT="2025-03-28T16:45:12.02Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{1CB70762-CB98-18A3-8B23-8B0C43552DB3}" done="0">
+    <text xml:space="preserve">heads/debug_profiling-0-gb9cee85 with "stylegan" environment
+re-measure with current commit
+</text>
+  </threadedComment>
+  <threadedComment ref="E18" dT="2024-12-03T17:44:41.53Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
     <text xml:space="preserve">TODO try upgrading and re-measuring
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:35:38.28Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{D60FF92D-CD85-77A7-BAF7-B50E5A8F386D}" done="0">
+    <text xml:space="preserve">heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_1_40_xpu"
+re-measured current commit, with current GPU driver
+</text>
+  </threadedComment>
+  <threadedComment ref="A4" dT="2024-12-03T16:35:38.28Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{0A840647-343D-ECD8-EE73-9B5128B511C0}" done="0">
+    <text xml:space="preserve">heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_3_110_xpu"
+torch 2.3.1+cxx11.abi
+</text>
+  </threadedComment>
+  <threadedComment ref="A5" dT="2024-12-03T16:08:51.51Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 on a VM instance on Intel Tiber Developer Cloud
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
+  <threadedComment ref="A6" dT="2024-12-03T16:36:13.13Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
+</text>
+  </threadedComment>
+  <threadedComment ref="A7" dT="2024-12-03T16:36:13.13Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{3D18DD77-473E-3CE6-83E6-86E80A773716}" done="0">
+    <text xml:space="preserve">heads/debug_profiling-0-gb9cee85 with "stylegan" environment
 </text>
   </threadedComment>
 </ThreadedComments>
@@ -3840,15 +5688,15 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{D8426B48-3D18-4E14-7890-79335D173E8D}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{296568FF-0662-2C9F-C581-89AAD6A06E95}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -3888,7 +5736,7 @@
       <c r="C2">
         <v>10.01</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>27.27</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -3896,214 +5744,335 @@
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4">
+        <v>7.2599999999999998</v>
+      </c>
+      <c r="C3" s="4">
+        <v>9.9800000000000004</v>
+      </c>
+      <c r="D3" s="2">
+        <v>27.23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3">
-        <v>6.4199999999999999</v>
-      </c>
-      <c r="C3">
-        <v>14.91</v>
-      </c>
-      <c r="D3">
-        <v>33.369999999999997</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6.8300000000000001</v>
+      </c>
+      <c r="C4" s="4">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="D4" s="2">
+        <v>21.140000000000001</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4">
-        <v>11.9</v>
-      </c>
-      <c r="C4">
-        <v>10.27</v>
-      </c>
-      <c r="D4">
-        <v>20.829999999999998</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="2">
-        <v>13.859999999999999</v>
-      </c>
-      <c r="C5" s="2">
-        <v>7.04</v>
+      <c r="B5">
+        <v>6.4199999999999999</v>
+      </c>
+      <c r="C5">
+        <v>14.91</v>
       </c>
       <c r="D5" s="2">
-        <v>36.68</v>
+        <v>33.369999999999997</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2">
-        <v>1.01</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.77</v>
+      <c r="B6">
+        <v>11.9</v>
+      </c>
+      <c r="C6">
+        <v>10.27</v>
       </c>
       <c r="D6" s="2">
-        <v>24.52</v>
+        <v>20.829999999999998</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6">
+        <v>12.630000000000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="D7" s="7">
+        <v>22.07</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="C7">
-        <v>0.92000000000000004</v>
-      </c>
-      <c r="D7">
-        <v>15.130000000000001</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8">
-        <v>0.23000000000000001</v>
-      </c>
-      <c r="C8">
-        <v>0.81999999999999995</v>
-      </c>
-      <c r="D8">
-        <v>22.699999999999999</v>
+      <c r="B8" s="4">
+        <v>13.859999999999999</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7.04</v>
+      </c>
+      <c r="D8" s="2">
+        <v>36.68</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1.01</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.77</v>
+      </c>
+      <c r="D9" s="2">
+        <v>24.52</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" t="s">
-        <v>14</v>
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1.01</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20.690000000000001</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="11" ht="14.25"/>
+    <row r="11" ht="14.25">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="C11">
+        <v>0.92000000000000004</v>
+      </c>
+      <c r="D11" s="2">
+        <v>15.130000000000001</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="12" ht="14.25">
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.26000000000000001</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.96999999999999997</v>
+      </c>
+      <c r="D12" s="7">
+        <v>16.02</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
+      <c r="B13">
+        <v>0.23000000000000001</v>
+      </c>
+      <c r="C13">
+        <v>0.81999999999999995</v>
+      </c>
+      <c r="D13" s="2">
+        <v>22.699999999999999</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="B15" t="s">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25"/>
+    <row r="17" ht="14.25">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
         <v>26</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C18" t="s">
         <v>27</v>
       </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22">
-        <f>C4/C7</f>
-        <v>11.163043478260869</v>
+    <row r="19" ht="14.25">
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23">
-        <f>C5/C8</f>
-        <v>8.5853658536585371</v>
+    <row r="20" ht="14.25">
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="24" ht="14.25">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24">
-        <f>C2/C6</f>
-        <v>5.6553672316384178</v>
+    <row r="24" ht="14.25"/>
+    <row r="25" ht="14.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="C26" t="str">
+        <f>C1</f>
+        <v>stylegan3-t</v>
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" t="s">
-        <v>32</v>
+      <c r="A27" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C27">
-        <f>C6/C7</f>
-        <v>1.9239130434782608</v>
+        <f>C6/C11</f>
+        <v>11.163043478260869</v>
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="3" t="s">
-        <v>33</v>
+      <c r="A28" t="s">
+        <v>38</v>
       </c>
       <c r="C28">
-        <f>C6/C8</f>
+        <f>C7/C12</f>
+        <v>11.237113402061857</v>
+      </c>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <f>C8/C13</f>
+        <v>8.5853658536585371</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <f>C2/C9</f>
+        <v>5.6553672316384178</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31">
+        <f>C4/C10</f>
+        <v>5.3085714285714278</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25"/>
+    <row r="33" ht="14.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33">
+        <f>C9/C11</f>
+        <v>1.9239130434782608</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34">
+        <f>C9/C13</f>
         <v>2.1585365853658538</v>
       </c>
     </row>
+    <row r="35" ht="14.25"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -4116,6 +6085,502 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="23.57421875"/>
+    <col bestFit="1" min="2" max="2" width="5.8515625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="21.00390625"/>
+    <col bestFit="1" min="4" max="4" width="35.140625"/>
+    <col customWidth="1" min="5" max="5" width="30.00390625"/>
+    <col bestFit="1" min="6" max="6" width="21.421875"/>
+    <col bestFit="1" min="7" max="7" width="4.7109375"/>
+    <col bestFit="1" min="8" max="8" width="5.28125"/>
+    <col bestFit="1" min="9" max="9" width="5.57421875"/>
+    <col bestFit="1" min="10" max="10" width="7.140625"/>
+    <col bestFit="1" min="11" max="11" width="5.28125"/>
+    <col bestFit="1" min="12" max="12" width="3.57421875"/>
+    <col bestFit="1" min="16" max="16" width="10.8515625"/>
+    <col customWidth="1" min="17" max="17" width="26.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="H1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2">
+        <v>9.5999999999999996</v>
+      </c>
+      <c r="I2">
+        <v>20.449999999999999</v>
+      </c>
+      <c r="J2">
+        <v>21.02</v>
+      </c>
+      <c r="K2">
+        <v>21.16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <v>13.41</v>
+      </c>
+      <c r="I3">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="J3">
+        <v>20.52</v>
+      </c>
+      <c r="K3">
+        <v>20.75</v>
+      </c>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4">
+        <v>13.720000000000001</v>
+      </c>
+      <c r="I4">
+        <v>19.859999999999999</v>
+      </c>
+      <c r="J4">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="K4">
+        <v>22.010000000000002</v>
+      </c>
+      <c r="L4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4">
+        <f>STDEV(H2:H4)/AVERAGE(H2:H4)*100</f>
+        <v>18.740282852691443</v>
+      </c>
+      <c r="N4">
+        <f>STDEV(I2:I4)/AVERAGE(I2:I4)*100</f>
+        <v>1.4638477867466417</v>
+      </c>
+      <c r="O4">
+        <f>STDEV(J2:J4)/AVERAGE(J2:J4)*100</f>
+        <v>4.2228980405069967</v>
+      </c>
+      <c r="P4">
+        <f>STDEV(K2:K4)/AVERAGE(K2:K4)*100</f>
+        <v>3.0163174010526634</v>
+      </c>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5">
+        <v>4.9100000000000001</v>
+      </c>
+      <c r="I5">
+        <v>6.7599999999999998</v>
+      </c>
+      <c r="J5">
+        <v>6.7999999999999998</v>
+      </c>
+      <c r="K5">
+        <v>6.8499999999999996</v>
+      </c>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6">
+        <v>5.2199999999999998</v>
+      </c>
+      <c r="I6">
+        <v>6.7800000000000002</v>
+      </c>
+      <c r="J6">
+        <v>6.8200000000000003</v>
+      </c>
+      <c r="K6">
+        <v>6.8600000000000003</v>
+      </c>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7">
+        <v>5.2000000000000002</v>
+      </c>
+      <c r="I7">
+        <v>6.7699999999999996</v>
+      </c>
+      <c r="J7">
+        <v>6.8099999999999996</v>
+      </c>
+      <c r="K7">
+        <v>6.8600000000000003</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="3">
+        <f>STDEV(H5:H7)/AVERAGE(H5:H7)*100</f>
+        <v>3.3951764330523408</v>
+      </c>
+      <c r="N7" s="3">
+        <f>STDEV(I5:I7)/AVERAGE(I5:I7)*100</f>
+        <v>0.14771048744461199</v>
+      </c>
+      <c r="O7" s="3">
+        <f>STDEV(J5:J7)/AVERAGE(J5:J7)*100</f>
+        <v>0.14684287812041455</v>
+      </c>
+      <c r="P7" s="3">
+        <f>STDEV(K5:K7)/AVERAGE(K5:K7)*100</f>
+        <v>0.084202761670831031</v>
+      </c>
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8">
+        <v>6.3600000000000003</v>
+      </c>
+      <c r="I8">
+        <v>9.1799999999999997</v>
+      </c>
+      <c r="J8">
+        <v>9.2599999999999998</v>
+      </c>
+      <c r="K8">
+        <v>9.3300000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9">
+        <v>6.3799999999999999</v>
+      </c>
+      <c r="I9">
+        <v>9.1699999999999999</v>
+      </c>
+      <c r="J9">
+        <v>9.2300000000000004</v>
+      </c>
+      <c r="K9">
+        <v>9.3399999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10">
+        <v>6.1699999999999999</v>
+      </c>
+      <c r="I10">
+        <v>9.1899999999999995</v>
+      </c>
+      <c r="J10">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="K10">
+        <v>9.3399999999999999</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="3">
+        <f>STDEV(H8:H10)/AVERAGE(H8:H10)*100</f>
+        <v>1.8387454945228685</v>
+      </c>
+      <c r="N10" s="3">
+        <f>STDEV(I8:I10)/AVERAGE(I8:I10)*100</f>
+        <v>0.10893246187363603</v>
+      </c>
+      <c r="O10" s="3">
+        <f>STDEV(J8:J10)/AVERAGE(J8:J10)*100</f>
+        <v>0.27187016331546948</v>
+      </c>
+      <c r="P10" s="3">
+        <f>STDEV(K8:K10)/AVERAGE(K8:K10)*100</f>
+        <v>0.061836872815738672</v>
+      </c>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11">
+      <c r="M11">
+        <f>MAX(M4:M10)</f>
+        <v>18.740282852691443</v>
+      </c>
+      <c r="N11">
+        <f>MAX(N4:N10)</f>
+        <v>1.4638477867466417</v>
+      </c>
+      <c r="O11">
+        <f>MAX(O4:O10)</f>
+        <v>4.2228980405069967</v>
+      </c>
+      <c r="P11">
+        <f>MAX(P4:P10)</f>
+        <v>3.0163174010526634</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="M12" s="3">
+        <f>AVERAGE(M5:M11)</f>
+        <v>7.9914015934222178</v>
+      </c>
+      <c r="N12" s="3">
+        <f>AVERAGE(N5:N11)</f>
+        <v>0.57349691202162989</v>
+      </c>
+      <c r="O12" s="3">
+        <f>AVERAGE(O5:O11)</f>
+        <v>1.5472036939809604</v>
+      </c>
+      <c r="P12" s="3">
+        <f>AVERAGE(P5:P11)</f>
+        <v>1.054119011846411</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="M14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:L11" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="E2:E11"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="Q2:Q10"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="13.28125"/>
@@ -4135,7 +6600,7 @@
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>7.4500000000000002</v>
@@ -4149,7 +6614,7 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>6.4199999999999999</v>
@@ -4163,7 +6628,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B4">
         <v>11.9</v>
@@ -4177,7 +6642,7 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/bench.xlsx
+++ b/bench.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="current" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="stddev of metrics" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="backup" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="profile sg3-t PVC" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="stddev of metrics" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="backup" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -352,6 +353,38 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={80F3E044-5FFD-2CA2-6416-75190749A912}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" xr:uid="{80F3E044-5FFD-2CA2-6416-75190749A912}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>user:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+sg3-t gpu-hotspots 2.3.110 PVC
+Apr 02 2025 21:10:41
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={FBA8A04F-1144-D4CE-3955-9139357F1DF7}</author>
     <author>tc={49BA0359-1DD6-6E69-0623-10EC65534207}</author>
     <author>tc={71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}</author>
@@ -425,7 +458,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="207">
   <si>
     <t>stylegan3-r</t>
   </si>
@@ -626,6 +659,348 @@
   </si>
   <si>
     <t xml:space="preserve">- when NOT using the custom kernels, Intel GPUs are significantly faster -&gt; mayby that's partially why we do not get such high speedups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source Computing Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instance Count</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, GB/sec</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Stalled</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XVE Threads Occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Threads Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU0 and ALU1 active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU0 and ALU2 active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU0 active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU1 active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU2 active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU0 Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU1 Instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU2 instructions</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU Barriers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU Atomics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Time [s]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is bias_act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is filtered_lrelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bias_act time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filtered_lrelu time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other time</t>
+  </si>
+  <si>
+    <t>[Unknown]</t>
+  </si>
+  <si>
+    <t>0s</t>
+  </si>
+  <si>
+    <t>0ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0 B </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bias_act_kernel_launch(bias_act_kernel_params)::{lambda(sycl::_V1::handler&amp;)#1}::operator()(sycl::_V1::handler&amp;) const::{lambda()#1}::operator()(void) const::{lambda()#2}::operator()(void) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t>0.000s</t>
+  </si>
+  <si>
+    <t>0.008ms</t>
+  </si>
+  <si>
+    <t>conv_reorder</t>
+  </si>
+  <si>
+    <t>0.242s</t>
+  </si>
+  <si>
+    <t>0.083ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DpcppElementwiseKernelWithIndexImplFunctor&lt;float, at::AtenIpexTypeXPU::impl::linspace_dpcpp_out_functor_2&lt;float&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.003ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::dpcpp_loops_launch_legacy_kernel_functor&lt;at::AtenIpexTypeXPU::BinaryFunctor&lt;float, float, float, at::AtenIpexTypeXPU::impl::DivFunctor&lt;float&gt;&gt;, float, OffsetCalculator&lt;(int)3, unsigned int, (bool)0&gt;, (int)3&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.005ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::dpcpp_loops_launch_legacy_kernel_functor&lt;at::AtenIpexTypeXPU::BinaryFunctor&lt;float, float, float, at::AtenIpexTypeXPU::impl::mul_kernel_dpcpp_functor&lt;float&gt;&gt;, float, OffsetCalculator&lt;(int)3, unsigned int, (bool)0&gt;, (int)3&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.050s</t>
+  </si>
+  <si>
+    <t>0.010ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::dpcpp_loops_launch_legacy_kernel_functor&lt;at::AtenIpexTypeXPU::impl::fill_kernel_dpcpp_functor&lt;float&gt;, float, OffsetCalculator&lt;(int)1, unsigned int, (bool)0&gt;, (int)1&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.001s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::dpcpp_loops_launch_legacy_kernel_functor&lt;at::impl::direct_copy_kernel_gpu_functor&lt;float&gt;, float, OffsetCalculator&lt;(int)2, unsigned int, (bool)0&gt;, (int)2&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.003s</t>
+  </si>
+  <si>
+    <t>0.011ms</t>
+  </si>
+  <si>
+    <t>gemm_kernel</t>
+  </si>
+  <si>
+    <t>0.016s</t>
+  </si>
+  <si>
+    <t>gen_conv</t>
+  </si>
+  <si>
+    <t>2.300s</t>
+  </si>
+  <si>
+    <t>2.323ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduce_kernel&lt;(int)1, at::AtenIpexTypeXPU::ReduceOp&lt;float, at::AtenIpexTypeXPU::func_wrapper_t&lt;float, at::AtenIpexTypeXPU::ReduceAddOps&lt;float&gt;&gt;, unsigned int, float, (int)4&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.018s</t>
+  </si>
+  <si>
+    <t>0.020ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduce_kernel&lt;(int)1, at::AtenIpexTypeXPU::ReduceOp&lt;float, at::AtenIpexTypeXPU::NormOps&lt;float, float&gt;, unsigned int, float, (int)4&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.002s</t>
+  </si>
+  <si>
+    <t>0.016ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduce_kernel&lt;(int)1, at::AtenIpexTypeXPU::ReduceOp&lt;float, at::AtenIpexTypeXPU::ReduceMeanOps&lt;float, float&gt;, unsigned int, float, (int)4&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.023s</t>
+  </si>
+  <si>
+    <t>0.012ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)0, (int)2, (int)12, (int)2, (int)12, (int)32, (int)46, (int)16, (int)10, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#1}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)0, (int)2, (int)12, (int)2, (int)12, (int)32, (int)46, (int)16, (int)10, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#2}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t>0.383s</t>
+  </si>
+  <si>
+    <t>0.646ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)0, (int)4, (int)24, (int)2, (int)12, (int)32, (int)51, (int)16, (int)5, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#1}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)0, (int)4, (int)24, (int)2, (int)12, (int)32, (int)51, (int)16, (int)5, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#2}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t>0.212s</t>
+  </si>
+  <si>
+    <t>0.642ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)3, (int)1, (int)1, (int)1, (int)1, (int)64, (int)178, (int)32, (int)0, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#1}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run_filtered_lrelu_kernel&lt;float, int, (bool)0, (bool)0, (int)3, (int)1, (int)1, (int)1, (int)1, (int)64, (int)178, (int)32, (int)0, (int)0&gt;(void, filtered_lrelu_kernel_params&amp;)::{lambda(sycl::_V1::handler&amp;)#2}::operator()(sycl::_V1::handler&amp;) const::{lambda(sycl::_V1::nd_item&lt;(int)3&gt;)#1}</t>
+  </si>
+  <si>
+    <t>0.014ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnrolledElementwiseKernelFunctor&lt;(int)4, at::impl::direct_copy_kernel_gpu_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, at::native::Memory::LoadWithCast&lt;(int)1, (bool)1&gt;, at::native::Memory::StoreWithCast&lt;(bool)1&gt;&gt;</t>
+  </si>
+  <si>
+    <t>0.029ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::AUnaryFunctor&lt;float, float, float, at::AtenIpexTypeXPU::impl::mul_kernel_dpcpp_functor&lt;float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.008s</t>
+  </si>
+  <si>
+    <t>0.006ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::AUnaryFunctor&lt;float, float, float, at::impl::AddKernelDpcppFunctor&lt;float, float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.004ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::BinaryFunctor&lt;float, float, float, at::AtenIpexTypeXPU::impl::mul_kernel_dpcpp_functor&lt;float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)3&gt;, OffsetCalculator&lt;(int)2, unsigned int, (bool)0&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::BinaryFunctor&lt;float, float, float, at::impl::AddKernelDpcppFunctor&lt;float, float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)3&gt;, OffsetCalculator&lt;(int)2, unsigned int, (bool)0&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.007ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::BinaryFunctor&lt;float, float, float, at::impl::AddKernelDpcppFunctor&lt;float, float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)3&gt;, TrivialOffsetCalculator&lt;(int)2, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::BUnaryFunctor&lt;float, float, float, at::AtenIpexTypeXPU::impl::MulFunctor&lt;float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::BUnaryFunctor&lt;float, float, float, at::impl::AddKernelDpcppFunctor&lt;float, float&gt;&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.004s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::clamp_min_max_functor&lt;float, float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::impl::fill_kernel_dpcpp_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)1&gt;, TrivialOffsetCalculator&lt;(int)0, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.002ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::neg_out_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)1&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::neg_out_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)2&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::pow_tensor_scalar_kernel_impl_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.024s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::rsqrt_kernel_xpu_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>0.015s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::AtenIpexTypeXPU::sin_out_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::impl::memcpyAsync_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)1&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::impl::memcpyAsync_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)2&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VectorizedElementwiseKernelFunctor&lt;at::impl::memcpyAsync_functor&lt;float&gt;, torch_ipex::xpu::dpcpp::Array&lt;char*, (int)2&gt;, TrivialOffsetCalculator&lt;(int)1, unsigned int&gt;, (int)4&gt;</t>
+  </si>
+  <si>
+    <t>zeCommandListAppendMemoryCopy</t>
+  </si>
+  <si>
+    <t>0.153s</t>
+  </si>
+  <si>
+    <t>0.069ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1 GB </t>
+  </si>
+  <si>
+    <t>zeCommandListAppendMemoryFill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7 MB </t>
   </si>
   <si>
     <t>min</t>
@@ -710,10 +1085,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss AM/PM"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -726,13 +1103,26 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -747,7 +1137,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
@@ -756,6 +1146,20 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -13171,7 +13575,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="user" id="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" userId="user" providerId="Teamlab"/>
+  <person displayName="user" id="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" userId="user" providerId="Teamlab"/>
 </personList>
 </file>
 
@@ -13667,74 +14071,74 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{5D1DD697-3B31-24C3-D1FC-4F10BC94625B}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 exact pytorch version: 2.1.0.post3+cxx11.abi
 </text>
   </threadedComment>
-  <threadedComment ref="A11" dT="2025-04-01T10:59:07.03Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{D300BCD4-AF64-1F2B-8C24-5B84F5440E4F}" done="0">
+  <threadedComment ref="A11" dT="2025-04-01T10:59:07.03Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{D300BCD4-AF64-1F2B-8C24-5B84F5440E4F}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gd9c04ad
 stylegan3_pytorch_2_3
 </text>
   </threadedComment>
-  <threadedComment ref="A14" dT="2025-04-01T09:08:33.34Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{A01B7651-90D1-9D61-E5CA-ED6EEA98DA46}" done="0">
+  <threadedComment ref="A14" dT="2025-04-01T09:08:33.34Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{A01B7651-90D1-9D61-E5CA-ED6EEA98DA46}" done="0">
     <text xml:space="preserve">heads/debug_profiling-2.1-0-g37d3e93
 ipex_2_1_40
 VM instance
 </text>
   </threadedComment>
-  <threadedComment ref="A15" dT="2025-04-01T09:08:33.34Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{9C780A3F-2882-4906-A15E-6397004551BF}" done="0">
+  <threadedComment ref="A15" dT="2025-04-01T09:08:33.34Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{9C780A3F-2882-4906-A15E-6397004551BF}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gd9c04ad
 ipex_2_3_110
 VM instance
 </text>
   </threadedComment>
-  <threadedComment ref="A17" dT="2025-03-28T16:45:12.02Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{1CB70762-CB98-18A3-8B23-8B0C43552DB3}" done="0">
+  <threadedComment ref="A17" dT="2025-03-28T16:45:12.02Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{1CB70762-CB98-18A3-8B23-8B0C43552DB3}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gb9cee85 with "stylegan" environment
 re-measure with current commit
 </text>
   </threadedComment>
-  <threadedComment ref="A19" dT="2025-04-01T10:58:41.53Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{7ED0FFCC-B7DA-8554-413C-5373D5E862EB}" done="0">
+  <threadedComment ref="A19" dT="2025-04-01T10:58:41.53Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{7ED0FFCC-B7DA-8554-413C-5373D5E862EB}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gd9c04ad
 stylegan3_pytorch_2_3
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:35:38.28Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{D60FF92D-CD85-77A7-BAF7-B50E5A8F386D}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:35:38.28Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{D60FF92D-CD85-77A7-BAF7-B50E5A8F386D}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_1_40_xpu"
 re-measured current commit, with current GPU driver
 </text>
   </threadedComment>
-  <threadedComment ref="E24" dT="2024-12-03T17:44:41.53Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
+  <threadedComment ref="E24" dT="2024-12-03T17:44:41.53Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{44FE1040-EA6E-1D7C-5CD3-EEAB189226D0}" done="1">
     <text xml:space="preserve">TODO try upgrading and re-measuring
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:35:38.28Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{0A840647-343D-ECD8-EE73-9B5128B511C0}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:35:38.28Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{0A840647-343D-ECD8-EE73-9B5128B511C0}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gdab3304 with "ENVNAME=stylegan3_2_3_110_xpu"
 torch 2.3.1+cxx11.abi
 </text>
   </threadedComment>
-  <threadedComment ref="A5" dT="2024-12-03T16:08:51.51Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
+  <threadedComment ref="A5" dT="2024-12-03T16:08:51.51Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{9885B1C3-AB22-94B7-30B7-E8A667F23725}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 on a VM instance on Intel Tiber Developer Cloud
 </text>
   </threadedComment>
-  <threadedComment ref="A6" dT="2025-04-01T09:07:41.05Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{152CC54A-CC3F-A8E8-3020-50D37FDCC26A}" done="0">
+  <threadedComment ref="A6" dT="2025-04-01T09:07:41.05Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{152CC54A-CC3F-A8E8-3020-50D37FDCC26A}" done="0">
     <text xml:space="preserve">heads/debug_profiling-2.1-0-g37d3e93
 ipex_2_1_40
 VM instance
 </text>
   </threadedComment>
-  <threadedComment ref="A7" dT="2025-04-01T09:07:41.05Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{02D5EC6F-3679-B832-F9F8-3AF034DC73B7}" done="0">
+  <threadedComment ref="A7" dT="2025-04-01T09:07:41.05Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{02D5EC6F-3679-B832-F9F8-3AF034DC73B7}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gd9c04ad
 ipex_2_3_110
 VM instance
 </text>
   </threadedComment>
-  <threadedComment ref="A8" dT="2024-12-03T16:36:13.13Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
+  <threadedComment ref="A8" dT="2024-12-03T16:36:13.13Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{07C5CB9B-011A-F201-BE01-B6ED5DCC747A}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
-  <threadedComment ref="A9" dT="2024-12-03T16:36:13.13Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{3D18DD77-473E-3CE6-83E6-86E80A773716}" done="0">
+  <threadedComment ref="A9" dT="2024-12-03T16:36:13.13Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{3D18DD77-473E-3CE6-83E6-86E80A773716}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-gb9cee85 with "stylegan" environment
 </text>
   </threadedComment>
@@ -13743,15 +14147,25 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
+  <threadedComment ref="A1" dT="2025-04-03T10:32:40.71Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{80F3E044-5FFD-2CA2-6416-75190749A912}" done="0">
+    <text xml:space="preserve">sg3-t gpu-hotspots 2.3.110 PVC
+Apr 02 2025 21:10:41
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-12-03T16:35:38.28Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{FBA8A04F-1144-D4CE-3955-9139357F1DF7}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "ENVNAME=stylegan3_2_1_40_xpu"
 </text>
   </threadedComment>
-  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
+  <threadedComment ref="A3" dT="2024-12-03T16:08:51.51Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{49BA0359-1DD6-6E69-0623-10EC65534207}" done="0">
     <text xml:space="preserve">9390a36a6b1ee05f376ece3fc065dfb77f459ded with "-O1" (which is in the commit)
 </text>
   </threadedComment>
-  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{7C2D51F0-BCC6-2781-B9BC-1466D8C2E91C}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
+  <threadedComment ref="A4" dT="2024-12-03T16:36:13.13Z" personId="{1452FA7C-63D6-74A7-8D8B-180D0CD860F0}" id="{71B80EF3-EE31-C54E-AB34-BCEA6BB0C751}" done="0">
     <text xml:space="preserve">heads/debug_profiling-0-g9390a36 with "stylegan" environment
 </text>
   </threadedComment>
@@ -14309,6 +14723,4517 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="44.421875"/>
+    <col bestFit="1" min="2" max="2" style="6" width="9.7109375"/>
+    <col bestFit="1" min="3" max="3" width="12.140625"/>
+    <col bestFit="1" min="4" max="4" width="13.7109375"/>
+    <col bestFit="1" min="5" max="5" width="5.28125"/>
+    <col bestFit="1" min="6" max="6" width="12.00390625"/>
+    <col bestFit="1" min="7" max="8" width="6.8515625"/>
+    <col bestFit="1" min="9" max="9" width="7.8515625"/>
+    <col bestFit="1" min="10" max="10" width="21.140625"/>
+    <col bestFit="1" min="11" max="11" width="24.28125"/>
+    <col bestFit="1" min="12" max="13" width="18.8515625"/>
+    <col bestFit="1" min="14" max="14" width="10.421875"/>
+    <col bestFit="1" min="15" max="15" width="12.140625"/>
+    <col bestFit="1" min="16" max="18" width="10.421875"/>
+    <col bestFit="1" min="19" max="19" width="15.7109375"/>
+    <col bestFit="1" min="20" max="20" width="17.8515625"/>
+    <col bestFit="1" min="21" max="21" width="16.00390625"/>
+    <col bestFit="1" min="22" max="22" width="15.7109375"/>
+    <col bestFit="1" min="23" max="23" width="15.57421875"/>
+    <col bestFit="1" min="24" max="24" width="7.8515625"/>
+    <col bestFit="1" min="25" max="26" width="7.28125"/>
+    <col bestFit="1" min="27" max="27" width="6.28125"/>
+    <col bestFit="1" min="28" max="28" width="11.421875"/>
+    <col bestFit="1" min="29" max="29" width="11.7109375"/>
+    <col bestFit="1" min="30" max="30" style="7" width="12.00390625"/>
+    <col bestFit="1" min="31" max="31" width="9.421875"/>
+    <col bestFit="1" min="32" max="32" width="13.140625"/>
+    <col bestFit="1" min="33" max="33" width="7.140625"/>
+    <col bestFit="1" min="34" max="34" width="12.00390625"/>
+    <col bestFit="1" min="35" max="35" width="15.7109375"/>
+    <col bestFit="1" min="36" max="36" width="9.7109375"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>83</v>
+      </c>
+      <c r="R1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W1" t="s">
+        <v>89</v>
+      </c>
+      <c r="X1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I2" s="8">
+        <v>0.997</v>
+      </c>
+      <c r="J2" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="K2" s="9">
+        <v>81358429</v>
+      </c>
+      <c r="L2" s="8">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="R2" s="10">
+        <v>0</v>
+      </c>
+      <c r="S2" s="9">
+        <v>14375973466</v>
+      </c>
+      <c r="T2" s="9">
+        <v>2632905879</v>
+      </c>
+      <c r="U2" s="9">
+        <v>80231520867</v>
+      </c>
+      <c r="V2" s="9">
+        <v>58102712209</v>
+      </c>
+      <c r="W2" s="9">
+        <v>1907064</v>
+      </c>
+      <c r="X2">
+        <v>2.5750000000000002</v>
+      </c>
+      <c r="Y2">
+        <v>1.155</v>
+      </c>
+      <c r="Z2">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="AA2">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="AB2" s="9">
+        <v>112471205</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="11">
+        <f>0+SUBSTITUTE(B2,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <f>1-AE2-AF2</f>
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <f>AE2*$AD2</f>
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <f>AF2*$AD2</f>
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <f>AG2*$AD2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="12" customFormat="1">
+      <c r="A3" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="12">
+        <v>2</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <v>1</v>
+      </c>
+      <c r="J3" s="14">
+        <v>0</v>
+      </c>
+      <c r="K3" s="15">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="M3" s="16">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14">
+        <v>0</v>
+      </c>
+      <c r="P3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>0</v>
+      </c>
+      <c r="R3" s="16">
+        <v>0</v>
+      </c>
+      <c r="S3" s="15">
+        <v>0</v>
+      </c>
+      <c r="T3" s="15">
+        <v>0</v>
+      </c>
+      <c r="U3" s="15">
+        <v>0</v>
+      </c>
+      <c r="V3" s="15">
+        <v>0</v>
+      </c>
+      <c r="W3" s="15">
+        <v>0</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="11">
+        <f>0+SUBSTITUTE(B3,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <f>1-AE3-AF3</f>
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <f>AE3*$AD3</f>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f>AF3*$AD3</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f>AG3*$AD3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2904</v>
+      </c>
+      <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="K4" s="9">
+        <v>30705047</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.057999999999999996</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.013000000000000001</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0.24100000000000002</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0.115</v>
+      </c>
+      <c r="R4" s="10">
+        <v>0</v>
+      </c>
+      <c r="S4" s="9">
+        <v>2153439372</v>
+      </c>
+      <c r="T4" s="9">
+        <v>135509549</v>
+      </c>
+      <c r="U4" s="9">
+        <v>39315030444</v>
+      </c>
+      <c r="V4" s="9">
+        <v>18699802729</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>374.69600000000003</v>
+      </c>
+      <c r="Y4">
+        <v>132.91999999999999</v>
+      </c>
+      <c r="Z4">
+        <v>93.299999999999997</v>
+      </c>
+      <c r="AA4">
+        <v>48.078000000000003</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>249728</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="11">
+        <f>0+SUBSTITUTE(B4,"s","")</f>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="AG4">
+        <f>1-AE4-AF4</f>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f>AE4*$AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <f>AF4*$AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <f>AG4*$AD4</f>
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5">
+        <v>132</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="11">
+        <f>0+SUBSTITUTE(B5,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <f>1-AE5-AF5</f>
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <f>AE5*$AD5</f>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f>AF5*$AD5</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f>AG5*$AD5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>49</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>0</v>
+      </c>
+      <c r="S6" s="9">
+        <v>1343</v>
+      </c>
+      <c r="T6">
+        <v>443</v>
+      </c>
+      <c r="U6" s="9">
+        <v>2457</v>
+      </c>
+      <c r="V6" s="9">
+        <v>6999</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.248</v>
+      </c>
+      <c r="Y6">
+        <v>0.035999999999999997</v>
+      </c>
+      <c r="Z6">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="AA6">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="AB6">
+        <v>96</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="11">
+        <f>0+SUBSTITUTE(B6,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f>1-AE6-AF6</f>
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <f>AE6*$AD6</f>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f>AF6*$AD6</f>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f>AG6*$AD6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="9">
+        <v>4753</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.034000000000000002</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0.91599999999999993</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0.068000000000000005</v>
+      </c>
+      <c r="K7" s="9">
+        <v>2285894</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0.001</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0.001</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0.027999999999999997</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9">
+        <v>158746076</v>
+      </c>
+      <c r="T7" s="9">
+        <v>35459544</v>
+      </c>
+      <c r="U7" s="9">
+        <v>152360436</v>
+      </c>
+      <c r="V7" s="9">
+        <v>937047387</v>
+      </c>
+      <c r="W7" s="9">
+        <v>4724</v>
+      </c>
+      <c r="X7">
+        <v>67.802999999999997</v>
+      </c>
+      <c r="Y7">
+        <v>38.603000000000002</v>
+      </c>
+      <c r="Z7">
+        <v>13.045999999999999</v>
+      </c>
+      <c r="AA7">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>202229</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="11">
+        <f>0+SUBSTITUTE(B7,"s","")</f>
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AG7">
+        <f>1-AE7-AF7</f>
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <f>AE7*$AD7</f>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f>AF7*$AD7</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f>AG7*$AD7</f>
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8">
+        <v>264</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>326</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9">
+        <v>5110</v>
+      </c>
+      <c r="T8" s="9">
+        <v>3218</v>
+      </c>
+      <c r="U8" s="9">
+        <v>10760</v>
+      </c>
+      <c r="V8" s="9">
+        <v>37432</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="Y8">
+        <v>0.053999999999999999</v>
+      </c>
+      <c r="Z8">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="AA8">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="AB8">
+        <v>192</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="11">
+        <f>0+SUBSTITUTE(B8,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG8">
+        <f>1-AE8-AF8</f>
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <f>AE8*$AD8</f>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <f>AF8*$AD8</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f>AG8*$AD8</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9">
+        <v>265</v>
+      </c>
+      <c r="E9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.032000000000000001</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.057999999999999996</v>
+      </c>
+      <c r="K9" s="9">
+        <v>178194</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O9" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>0.028999999999999998</v>
+      </c>
+      <c r="R9" s="10">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9">
+        <v>16091048</v>
+      </c>
+      <c r="T9" s="9">
+        <v>3841682</v>
+      </c>
+      <c r="U9" s="9">
+        <v>5706129</v>
+      </c>
+      <c r="V9" s="9">
+        <v>104222359</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>97.647999999999996</v>
+      </c>
+      <c r="Y9">
+        <v>62.136000000000003</v>
+      </c>
+      <c r="Z9">
+        <v>9.9960000000000004</v>
+      </c>
+      <c r="AA9">
+        <v>32.813000000000002</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>1728</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="11">
+        <f>0+SUBSTITUTE(B9,"s","")</f>
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="AG9">
+        <f>1-AE9-AF9</f>
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <f>AE9*$AD9</f>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f>AF9*$AD9</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f>AG9*$AD9</f>
+        <v>0.0030000000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1520</v>
+      </c>
+      <c r="E10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.027999999999999997</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.95299999999999996</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.033000000000000002</v>
+      </c>
+      <c r="K10" s="9">
+        <v>419690</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0.0080000000000000002</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="R10" s="10">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9">
+        <v>17405921</v>
+      </c>
+      <c r="T10" s="9">
+        <v>6067092</v>
+      </c>
+      <c r="U10" s="9">
+        <v>83455116</v>
+      </c>
+      <c r="V10" s="9">
+        <v>105216702</v>
+      </c>
+      <c r="W10" s="9">
+        <v>3553</v>
+      </c>
+      <c r="X10">
+        <v>33.719999999999999</v>
+      </c>
+      <c r="Y10">
+        <v>15.419</v>
+      </c>
+      <c r="Z10">
+        <v>2.3100000000000001</v>
+      </c>
+      <c r="AA10">
+        <v>10.742000000000001</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>91992</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="11">
+        <f>0+SUBSTITUTE(B10,"s","")</f>
+        <v>0.016</v>
+      </c>
+      <c r="AG10">
+        <f>1-AE10-AF10</f>
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <f>AE10*$AD10</f>
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <f>AF10*$AD10</f>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f>AG10*$AD10</f>
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11">
+        <v>990</v>
+      </c>
+      <c r="E11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.82200000000000006</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.08199999999999999</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0.096000000000000002</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="K11" s="9">
+        <v>69281964</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0.028999999999999998</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="R11" s="10">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9">
+        <v>45607314543</v>
+      </c>
+      <c r="T11" s="9">
+        <v>2606254007</v>
+      </c>
+      <c r="U11" s="9">
+        <v>1155506554902</v>
+      </c>
+      <c r="V11" s="9">
+        <v>405437435521</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11" s="17">
+        <v>1052.1130000000001</v>
+      </c>
+      <c r="Y11">
+        <v>40.718000000000004</v>
+      </c>
+      <c r="Z11">
+        <v>23.821999999999999</v>
+      </c>
+      <c r="AA11">
+        <v>35.320999999999998</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>8579839</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="11">
+        <f>0+SUBSTITUTE(B11,"s","")</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AG11">
+        <f>1-AE11-AF11</f>
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <f>AE11*$AD11</f>
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <f>AF11*$AD11</f>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f>AG11*$AD11</f>
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12">
+        <v>924</v>
+      </c>
+      <c r="E12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.031</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.044000000000000004</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0.92599999999999993</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="K12" s="9">
+        <v>734478</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0.026000000000000002</v>
+      </c>
+      <c r="R12" s="10">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9">
+        <v>43284106</v>
+      </c>
+      <c r="T12" s="9">
+        <v>9760446</v>
+      </c>
+      <c r="U12" s="9">
+        <v>36581873</v>
+      </c>
+      <c r="V12" s="9">
+        <v>279398165</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>49.109000000000002</v>
+      </c>
+      <c r="Y12">
+        <v>31.129000000000001</v>
+      </c>
+      <c r="Z12">
+        <v>8.3900000000000006</v>
+      </c>
+      <c r="AA12">
+        <v>12.223000000000001</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>21000</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="11">
+        <f>0+SUBSTITUTE(B12,"s","")</f>
+        <v>0.017999999999999999</v>
+      </c>
+      <c r="AG12">
+        <f>1-AE12-AF12</f>
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <f>AE12*$AD12</f>
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <f>AF12*$AD12</f>
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <f>AG12*$AD12</f>
+        <v>0.017999999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13">
+        <v>132</v>
+      </c>
+      <c r="E13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>346</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
+        <v>0</v>
+      </c>
+      <c r="S13" s="9">
+        <v>5670</v>
+      </c>
+      <c r="T13" s="9">
+        <v>2656</v>
+      </c>
+      <c r="U13" s="9">
+        <v>7002</v>
+      </c>
+      <c r="V13" s="9">
+        <v>46070</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>1.21</v>
+      </c>
+      <c r="Y13">
+        <v>0.029000000000000001</v>
+      </c>
+      <c r="Z13">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="AA13">
+        <v>0.11</v>
+      </c>
+      <c r="AB13">
+        <v>192</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="11">
+        <f>0+SUBSTITUTE(B13,"s","")</f>
+        <v>0.002</v>
+      </c>
+      <c r="AG13">
+        <f>1-AE13-AF13</f>
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <f>AE13*$AD13</f>
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <f>AF13*$AD13</f>
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <f>AG13*$AD13</f>
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1849</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.0090000000000000011</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.031</v>
+      </c>
+      <c r="I14" s="10">
+        <v>0.95999999999999996</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.027999999999999997</v>
+      </c>
+      <c r="K14" s="9">
+        <v>565048</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="O14" s="10">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0.0060000000000000001</v>
+      </c>
+      <c r="R14" s="10">
+        <v>0</v>
+      </c>
+      <c r="S14" s="9">
+        <v>33969743</v>
+      </c>
+      <c r="T14" s="9">
+        <v>7118288</v>
+      </c>
+      <c r="U14" s="9">
+        <v>42550745</v>
+      </c>
+      <c r="V14" s="9">
+        <v>99654229</v>
+      </c>
+      <c r="W14" s="9">
+        <v>10638</v>
+      </c>
+      <c r="X14">
+        <v>23.163</v>
+      </c>
+      <c r="Y14">
+        <v>15.269</v>
+      </c>
+      <c r="Z14">
+        <v>11.564</v>
+      </c>
+      <c r="AA14">
+        <v>11.798999999999999</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>226118</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="11">
+        <f>0+SUBSTITUTE(B14,"s","")</f>
+        <v>0.023</v>
+      </c>
+      <c r="AG14">
+        <f>1-AE14-AF14</f>
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <f>AE14*$AD14</f>
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <f>AF14*$AD14</f>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f>AG14*$AD14</f>
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="15" s="12" customFormat="1">
+      <c r="A15" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="12">
+        <v>594</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="I15" s="14">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="K15" s="15">
+        <v>719310</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0.072999999999999995</v>
+      </c>
+      <c r="M15" s="16">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14">
+        <v>0.017000000000000001</v>
+      </c>
+      <c r="O15" s="14">
+        <v>0.001</v>
+      </c>
+      <c r="P15" s="14">
+        <v>0.34600000000000003</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>0.153</v>
+      </c>
+      <c r="R15" s="16">
+        <v>0</v>
+      </c>
+      <c r="S15" s="15">
+        <v>38082482</v>
+      </c>
+      <c r="T15" s="15">
+        <v>1769135</v>
+      </c>
+      <c r="U15" s="15">
+        <v>763306227</v>
+      </c>
+      <c r="V15" s="15">
+        <v>337970486</v>
+      </c>
+      <c r="W15" s="12">
+        <v>0</v>
+      </c>
+      <c r="X15" s="12">
+        <v>836.26400000000001</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>294.47699999999998</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>139.69200000000001</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>93.195999999999998</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="11">
+        <f>0+SUBSTITUTE(B15,"s","")</f>
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <f>1-AE15-AF15</f>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f>AE15*$AD15</f>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f>AF15*$AD15</f>
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="AJ15">
+        <f>AG15*$AD15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="12" customFormat="1">
+      <c r="A16" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="12">
+        <v>594</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0.36200000000000004</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="K16" s="15">
+        <v>20754419</v>
+      </c>
+      <c r="L16" s="14">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0</v>
+      </c>
+      <c r="N16" s="14">
+        <v>0.083000000000000004</v>
+      </c>
+      <c r="O16" s="14">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="P16" s="14">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>0.19899999999999998</v>
+      </c>
+      <c r="R16" s="16">
+        <v>0</v>
+      </c>
+      <c r="S16" s="15">
+        <v>21510205232</v>
+      </c>
+      <c r="T16" s="15">
+        <v>4753661188</v>
+      </c>
+      <c r="U16" s="15">
+        <v>42084493248</v>
+      </c>
+      <c r="V16" s="15">
+        <v>51767078959</v>
+      </c>
+      <c r="W16" s="15">
+        <v>1598425</v>
+      </c>
+      <c r="X16" s="12">
+        <v>152.77799999999999</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>156.005</v>
+      </c>
+      <c r="Z16" s="12">
+        <v>67.016999999999996</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>94.007999999999996</v>
+      </c>
+      <c r="AB16" s="15">
+        <v>207017134</v>
+      </c>
+      <c r="AC16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="11">
+        <f>0+SUBSTITUTE(B16,"s","")</f>
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AF16" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <f>1-AE16-AF16</f>
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f>AE16*$AD16</f>
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <f>AF16*$AD16</f>
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AJ16">
+        <f>AG16*$AD16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="12" customFormat="1">
+      <c r="A17" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="12">
+        <v>330</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0.248</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="K17" s="15">
+        <v>372057</v>
+      </c>
+      <c r="L17" s="14">
+        <v>0.088000000000000009</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0</v>
+      </c>
+      <c r="N17" s="14">
+        <v>0.019</v>
+      </c>
+      <c r="O17" s="14">
+        <v>0.001</v>
+      </c>
+      <c r="P17" s="14">
+        <v>0.42100000000000004</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="R17" s="16">
+        <v>0</v>
+      </c>
+      <c r="S17" s="15">
+        <v>17395732</v>
+      </c>
+      <c r="T17" s="15">
+        <v>743559</v>
+      </c>
+      <c r="U17" s="15">
+        <v>383360250</v>
+      </c>
+      <c r="V17" s="15">
+        <v>155483390</v>
+      </c>
+      <c r="W17" s="12">
+        <v>0</v>
+      </c>
+      <c r="X17" s="12">
+        <v>613.37800000000004</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>166.75999999999999</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>50.718000000000004</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>18.751999999999999</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="11">
+        <f>0+SUBSTITUTE(B17,"s","")</f>
+        <v>0.002</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <f>1-AE17-AF17</f>
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <f>AE17*$AD17</f>
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <f>AF17*$AD17</f>
+        <v>0.002</v>
+      </c>
+      <c r="AJ17">
+        <f>AG17*$AD17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="12" customFormat="1">
+      <c r="A18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="12">
+        <v>330</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="K18" s="15">
+        <v>18219699</v>
+      </c>
+      <c r="L18" s="14">
+        <v>0.047</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0</v>
+      </c>
+      <c r="N18" s="16">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="O18" s="14">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="P18" s="14">
+        <v>0.217</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="R18" s="16">
+        <v>0</v>
+      </c>
+      <c r="S18" s="15">
+        <v>13096082382</v>
+      </c>
+      <c r="T18" s="15">
+        <v>2241058751</v>
+      </c>
+      <c r="U18" s="15">
+        <v>31452929305</v>
+      </c>
+      <c r="V18" s="15">
+        <v>29034149880</v>
+      </c>
+      <c r="W18" s="15">
+        <v>1941573</v>
+      </c>
+      <c r="X18" s="12">
+        <v>143.98400000000001</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>201.309</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>42.189</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>84.021000000000001</v>
+      </c>
+      <c r="AB18" s="15">
+        <v>154394164</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="11">
+        <f>0+SUBSTITUTE(B18,"s","")</f>
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <f>1-AE18-AF18</f>
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <f>AE18*$AD18</f>
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <f>AF18*$AD18</f>
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="AJ18">
+        <f>AG18*$AD18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="12" customFormat="1">
+      <c r="A19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="12">
+        <v>66</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="16">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16">
+        <v>1</v>
+      </c>
+      <c r="J19" s="16">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="16">
+        <v>0</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0</v>
+      </c>
+      <c r="N19" s="16">
+        <v>0</v>
+      </c>
+      <c r="O19" s="16">
+        <v>0</v>
+      </c>
+      <c r="P19" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16">
+        <v>0</v>
+      </c>
+      <c r="S19" s="12">
+        <v>0</v>
+      </c>
+      <c r="T19" s="12">
+        <v>0</v>
+      </c>
+      <c r="U19" s="12">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12">
+        <v>0</v>
+      </c>
+      <c r="W19" s="12">
+        <v>0</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="11">
+        <f>0+SUBSTITUTE(B19,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <f>1-AE19-AF19</f>
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <f>AE19*$AD19</f>
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <f>AF19*$AD19</f>
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <f>AG19*$AD19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="12" customFormat="1">
+      <c r="A20" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="12">
+        <v>66</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16">
+        <v>1</v>
+      </c>
+      <c r="J20" s="16">
+        <v>0</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
+      <c r="L20" s="16">
+        <v>0</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0</v>
+      </c>
+      <c r="N20" s="16">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16">
+        <v>0</v>
+      </c>
+      <c r="P20" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>0</v>
+      </c>
+      <c r="R20" s="16">
+        <v>0</v>
+      </c>
+      <c r="S20" s="12">
+        <v>0</v>
+      </c>
+      <c r="T20" s="12">
+        <v>0</v>
+      </c>
+      <c r="U20" s="12">
+        <v>0</v>
+      </c>
+      <c r="V20" s="12">
+        <v>0</v>
+      </c>
+      <c r="W20" s="12">
+        <v>0</v>
+      </c>
+      <c r="X20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="11">
+        <f>0+SUBSTITUTE(B20,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AF20" s="12">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <f>1-AE20-AF20</f>
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <f>AE20*$AD20</f>
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <f>AF20*$AD20</f>
+        <v>0.001</v>
+      </c>
+      <c r="AJ20">
+        <f>AG20*$AD20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21">
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.031</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.072000000000000008</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.088000000000000009</v>
+      </c>
+      <c r="K21" s="9">
+        <v>170694</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="M21" s="10">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0.013000000000000001</v>
+      </c>
+      <c r="R21" s="10">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9">
+        <v>5675300</v>
+      </c>
+      <c r="T21" s="9">
+        <v>1335851</v>
+      </c>
+      <c r="U21" s="9">
+        <v>33037008</v>
+      </c>
+      <c r="V21" s="9">
+        <v>24220145</v>
+      </c>
+      <c r="W21" s="9">
+        <v>9777</v>
+      </c>
+      <c r="X21">
+        <v>142.32499999999999</v>
+      </c>
+      <c r="Y21">
+        <v>70.817999999999998</v>
+      </c>
+      <c r="Z21">
+        <v>21.003</v>
+      </c>
+      <c r="AA21">
+        <v>59.353999999999999</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>9216</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="11">
+        <f>0+SUBSTITUTE(B21,"s","")</f>
+        <v>0.002</v>
+      </c>
+      <c r="AG21">
+        <f>1-AE21-AF21</f>
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <f>AE21*$AD21</f>
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <f>AF21*$AD21</f>
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <f>AG21*$AD21</f>
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1454</v>
+      </c>
+      <c r="E22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.050999999999999997</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.026000000000000002</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.92299999999999993</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.057999999999999996</v>
+      </c>
+      <c r="K22" s="9">
+        <v>147771</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.0090000000000000011</v>
+      </c>
+      <c r="M22" s="10">
+        <v>0</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0.036000000000000004</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0.022000000000000002</v>
+      </c>
+      <c r="R22" s="10">
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <v>24225533</v>
+      </c>
+      <c r="T22" s="9">
+        <v>5510561</v>
+      </c>
+      <c r="U22" s="9">
+        <v>203839895</v>
+      </c>
+      <c r="V22" s="9">
+        <v>120462407</v>
+      </c>
+      <c r="W22" s="9">
+        <v>7838</v>
+      </c>
+      <c r="X22">
+        <v>129.87899999999999</v>
+      </c>
+      <c r="Y22">
+        <v>73.900999999999996</v>
+      </c>
+      <c r="Z22">
+        <v>15.565</v>
+      </c>
+      <c r="AA22">
+        <v>70.099000000000004</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>193502</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="11">
+        <f>0+SUBSTITUTE(B22,"s","")</f>
+        <v>0.0080000000000000002</v>
+      </c>
+      <c r="AG22">
+        <f>1-AE22-AF22</f>
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <f>AE22*$AD22</f>
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <f>AF22*$AD22</f>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <f>AG22*$AD22</f>
+        <v>0.0080000000000000002</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>0</v>
+      </c>
+      <c r="R23" s="10">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="11">
+        <f>0+SUBSTITUTE(B23,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <f>1-AE23-AF23</f>
+        <v>1</v>
+      </c>
+      <c r="AH23">
+        <f>AE23*$AD23</f>
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <f>AF23*$AD23</f>
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <f>AG23*$AD23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0.024</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0.050999999999999997</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.064000000000000001</v>
+      </c>
+      <c r="K24" s="9">
+        <v>86320</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="O24" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P24" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>0.021000000000000001</v>
+      </c>
+      <c r="R24" s="10">
+        <v>0</v>
+      </c>
+      <c r="S24" s="9">
+        <v>1883399</v>
+      </c>
+      <c r="T24" s="9">
+        <v>1032470</v>
+      </c>
+      <c r="U24" s="9">
+        <v>2201427</v>
+      </c>
+      <c r="V24" s="9">
+        <v>19132017</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>96.545000000000002</v>
+      </c>
+      <c r="Y24">
+        <v>66.185000000000002</v>
+      </c>
+      <c r="Z24">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="AA24">
+        <v>9.1159999999999997</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="11">
+        <f>0+SUBSTITUTE(B24,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <f>1-AE24-AF24</f>
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <f>AE24*$AD24</f>
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <f>AF24*$AD24</f>
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <f>AG24*$AD24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25">
+        <v>66</v>
+      </c>
+      <c r="E25" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="I25" s="8">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0.037000000000000005</v>
+      </c>
+      <c r="K25" s="9">
+        <v>51646</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0</v>
+      </c>
+      <c r="M25" s="10">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="R25" s="10">
+        <v>0</v>
+      </c>
+      <c r="S25" s="9">
+        <v>1246046</v>
+      </c>
+      <c r="T25" s="9">
+        <v>783707</v>
+      </c>
+      <c r="U25" s="9">
+        <v>687734</v>
+      </c>
+      <c r="V25" s="9">
+        <v>16760840</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>44.960999999999999</v>
+      </c>
+      <c r="Y25">
+        <v>35.405999999999999</v>
+      </c>
+      <c r="Z25">
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="AA25">
+        <v>9.4920000000000009</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="11">
+        <f>0+SUBSTITUTE(B25,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <f>1-AE25-AF25</f>
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <f>AE25*$AD25</f>
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <f>AF25*$AD25</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <f>AG25*$AD25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26">
+        <v>66</v>
+      </c>
+      <c r="E26" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I26" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J26" s="10">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>136</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
+        <v>0</v>
+      </c>
+      <c r="P26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>0</v>
+      </c>
+      <c r="R26" s="10">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>982</v>
+      </c>
+      <c r="T26">
+        <v>800</v>
+      </c>
+      <c r="U26">
+        <v>568</v>
+      </c>
+      <c r="V26" s="9">
+        <v>9020</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>2.6549999999999998</v>
+      </c>
+      <c r="Y26">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z26">
+        <v>0.52000000000000002</v>
+      </c>
+      <c r="AA26">
+        <v>0.121</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="11">
+        <f>0+SUBSTITUTE(B26,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <f>1-AE26-AF26</f>
+        <v>1</v>
+      </c>
+      <c r="AH26">
+        <f>AE26*$AD26</f>
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <f>AF26*$AD26</f>
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <f>AG26*$AD26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27">
+        <v>264</v>
+      </c>
+      <c r="E27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>382</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10">
+        <v>0</v>
+      </c>
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>0</v>
+      </c>
+      <c r="R27" s="10">
+        <v>0</v>
+      </c>
+      <c r="S27" s="9">
+        <v>5026</v>
+      </c>
+      <c r="T27" s="9">
+        <v>5199</v>
+      </c>
+      <c r="U27" s="9">
+        <v>14398</v>
+      </c>
+      <c r="V27" s="9">
+        <v>55404</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>1.7709999999999999</v>
+      </c>
+      <c r="Y27">
+        <v>0.043999999999999997</v>
+      </c>
+      <c r="Z27">
+        <v>0.311</v>
+      </c>
+      <c r="AA27">
+        <v>0.070999999999999994</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="11">
+        <f>0+SUBSTITUTE(B27,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG27">
+        <f>1-AE27-AF27</f>
+        <v>1</v>
+      </c>
+      <c r="AH27">
+        <f>AE27*$AD27</f>
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <f>AF27*$AD27</f>
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <f>AG27*$AD27</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1055</v>
+      </c>
+      <c r="E28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.027999999999999997</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0.044000000000000004</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0.92799999999999994</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0.057000000000000002</v>
+      </c>
+      <c r="K28" s="9">
+        <v>206022</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O28" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="R28" s="10">
+        <v>0</v>
+      </c>
+      <c r="S28" s="9">
+        <v>11962184</v>
+      </c>
+      <c r="T28" s="9">
+        <v>2796659</v>
+      </c>
+      <c r="U28" s="9">
+        <v>5231948</v>
+      </c>
+      <c r="V28" s="9">
+        <v>78039854</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>76.456999999999994</v>
+      </c>
+      <c r="Y28">
+        <v>44.158000000000001</v>
+      </c>
+      <c r="Z28">
+        <v>12.364000000000001</v>
+      </c>
+      <c r="AA28">
+        <v>11.942</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>4282</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="11">
+        <f>0+SUBSTITUTE(B28,"s","")</f>
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="AG28">
+        <f>1-AE28-AF28</f>
+        <v>1</v>
+      </c>
+      <c r="AH28">
+        <f>AE28*$AD28</f>
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <f>AF28*$AD28</f>
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <f>AG28*$AD28</f>
+        <v>0.0040000000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29">
+        <v>130</v>
+      </c>
+      <c r="E29" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0.055</v>
+      </c>
+      <c r="H29" s="8">
+        <v>0.122</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0.158</v>
+      </c>
+      <c r="K29" s="9">
+        <v>47403</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O29" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0.039</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>0.018000000000000002</v>
+      </c>
+      <c r="R29" s="10">
+        <v>0</v>
+      </c>
+      <c r="S29" s="9">
+        <v>1729537</v>
+      </c>
+      <c r="T29" s="9">
+        <v>271890</v>
+      </c>
+      <c r="U29" s="9">
+        <v>17646789</v>
+      </c>
+      <c r="V29" s="9">
+        <v>8099266</v>
+      </c>
+      <c r="W29" s="9">
+        <v>2301</v>
+      </c>
+      <c r="X29">
+        <v>166.76900000000001</v>
+      </c>
+      <c r="Y29">
+        <v>57.314</v>
+      </c>
+      <c r="Z29">
+        <v>44.645000000000003</v>
+      </c>
+      <c r="AA29">
+        <v>68.081000000000003</v>
+      </c>
+      <c r="AB29" s="9">
+        <v>2304</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="11">
+        <f>0+SUBSTITUTE(B29,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG29">
+        <f>1-AE29-AF29</f>
+        <v>1</v>
+      </c>
+      <c r="AH29">
+        <f>AE29*$AD29</f>
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <f>AF29*$AD29</f>
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <f>AG29*$AD29</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30">
+        <v>462</v>
+      </c>
+      <c r="E30" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0.065000000000000002</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="K30" s="9">
+        <v>49480</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0.0040000000000000001</v>
+      </c>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8">
+        <v>0.037000000000000005</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>0.028999999999999998</v>
+      </c>
+      <c r="R30" s="10">
+        <v>0</v>
+      </c>
+      <c r="S30" s="9">
+        <v>1841320</v>
+      </c>
+      <c r="T30" s="9">
+        <v>50160</v>
+      </c>
+      <c r="U30" s="9">
+        <v>17060332</v>
+      </c>
+      <c r="V30" s="9">
+        <v>13290698</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>141.227</v>
+      </c>
+      <c r="Y30">
+        <v>67.242999999999995</v>
+      </c>
+      <c r="Z30">
+        <v>53.313000000000002</v>
+      </c>
+      <c r="AA30">
+        <v>46.707999999999998</v>
+      </c>
+      <c r="AB30">
+        <v>96</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="11">
+        <f>0+SUBSTITUTE(B30,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG30">
+        <f>1-AE30-AF30</f>
+        <v>1</v>
+      </c>
+      <c r="AH30">
+        <f>AE30*$AD30</f>
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <f>AF30*$AD30</f>
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <f>AG30*$AD30</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31">
+        <v>132</v>
+      </c>
+      <c r="E31" t="s">
+        <v>104</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>379</v>
+      </c>
+      <c r="L31" s="10">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10">
+        <v>0</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>0</v>
+      </c>
+      <c r="R31" s="10">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9">
+        <v>4563</v>
+      </c>
+      <c r="T31" s="9">
+        <v>2464</v>
+      </c>
+      <c r="U31" s="9">
+        <v>7726</v>
+      </c>
+      <c r="V31" s="9">
+        <v>25413</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>1.1779999999999999</v>
+      </c>
+      <c r="Y31">
+        <v>0.053999999999999999</v>
+      </c>
+      <c r="Z31">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="AA31">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="AB31">
+        <v>288</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="11">
+        <f>0+SUBSTITUTE(B31,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG31">
+        <f>1-AE31-AF31</f>
+        <v>1</v>
+      </c>
+      <c r="AH31">
+        <f>AE31*$AD31</f>
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <f>AF31*$AD31</f>
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <f>AG31*$AD31</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I32" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>129</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10">
+        <v>0</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>0</v>
+      </c>
+      <c r="R32" s="10">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9">
+        <v>1451</v>
+      </c>
+      <c r="T32">
+        <v>848</v>
+      </c>
+      <c r="U32" s="9">
+        <v>2547</v>
+      </c>
+      <c r="V32" s="9">
+        <v>8432</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="Y32">
+        <v>0.039</v>
+      </c>
+      <c r="Z32">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="AA32">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="AB32">
+        <v>96</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="11">
+        <f>0+SUBSTITUTE(B32,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <f>1-AE32-AF32</f>
+        <v>1</v>
+      </c>
+      <c r="AH32">
+        <f>AE32*$AD32</f>
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <f>AF32*$AD32</f>
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <f>AG32*$AD32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="9">
+        <v>2773</v>
+      </c>
+      <c r="E33" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0.013999999999999999</v>
+      </c>
+      <c r="H33" s="8">
+        <v>0.027999999999999997</v>
+      </c>
+      <c r="I33" s="8">
+        <v>0.95799999999999996</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0.033000000000000002</v>
+      </c>
+      <c r="K33" s="9">
+        <v>688169</v>
+      </c>
+      <c r="L33" s="10">
+        <v>0</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8">
+        <v>0.002</v>
+      </c>
+      <c r="O33" s="10">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>0.011000000000000001</v>
+      </c>
+      <c r="R33" s="10">
+        <v>0</v>
+      </c>
+      <c r="S33" s="9">
+        <v>33198240</v>
+      </c>
+      <c r="T33" s="9">
+        <v>7218250</v>
+      </c>
+      <c r="U33" s="9">
+        <v>58346377</v>
+      </c>
+      <c r="V33" s="9">
+        <v>199064728</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>36.316000000000003</v>
+      </c>
+      <c r="Y33">
+        <v>19.605</v>
+      </c>
+      <c r="Z33">
+        <v>10.333</v>
+      </c>
+      <c r="AA33">
+        <v>13.257</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>48334</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="11">
+        <f>0+SUBSTITUTE(B33,"s","")</f>
+        <v>0.024</v>
+      </c>
+      <c r="AG33">
+        <f>1-AE33-AF33</f>
+        <v>1</v>
+      </c>
+      <c r="AH33">
+        <f>AE33*$AD33</f>
+        <v>0</v>
+      </c>
+      <c r="AI33">
+        <f>AF33*$AD33</f>
+        <v>0</v>
+      </c>
+      <c r="AJ33">
+        <f>AG33*$AD33</f>
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="9">
+        <v>3763</v>
+      </c>
+      <c r="E34" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34" s="8">
+        <v>0.034000000000000002</v>
+      </c>
+      <c r="H34" s="8">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0.93099999999999994</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="K34" s="9">
+        <v>509006</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0.0030000000000000001</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0</v>
+      </c>
+      <c r="N34" s="8">
+        <v>0.0050000000000000001</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0.019</v>
+      </c>
+      <c r="R34" s="10">
+        <v>0</v>
+      </c>
+      <c r="S34" s="9">
+        <v>84586107</v>
+      </c>
+      <c r="T34" s="9">
+        <v>18239917</v>
+      </c>
+      <c r="U34" s="9">
+        <v>237113425</v>
+      </c>
+      <c r="V34" s="9">
+        <v>298695284</v>
+      </c>
+      <c r="W34" s="9">
+        <v>22480</v>
+      </c>
+      <c r="X34">
+        <v>86.682000000000002</v>
+      </c>
+      <c r="Y34">
+        <v>65.221999999999994</v>
+      </c>
+      <c r="Z34">
+        <v>20.545000000000002</v>
+      </c>
+      <c r="AA34">
+        <v>58.543999999999997</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>763660</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="11">
+        <f>0+SUBSTITUTE(B34,"s","")</f>
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="AG34">
+        <f>1-AE34-AF34</f>
+        <v>1</v>
+      </c>
+      <c r="AH34">
+        <f>AE34*$AD34</f>
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <f>AF34*$AD34</f>
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <f>AG34*$AD34</f>
+        <v>0.014999999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>171</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35">
+        <v>66</v>
+      </c>
+      <c r="E35" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>0</v>
+      </c>
+      <c r="O35" s="10">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>0</v>
+      </c>
+      <c r="R35" s="10">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="11">
+        <f>0+SUBSTITUTE(B35,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG35">
+        <f>1-AE35-AF35</f>
+        <v>1</v>
+      </c>
+      <c r="AH35">
+        <f>AE35*$AD35</f>
+        <v>0</v>
+      </c>
+      <c r="AI35">
+        <f>AF35*$AD35</f>
+        <v>0</v>
+      </c>
+      <c r="AJ35">
+        <f>AG35*$AD35</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>172</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36">
+        <v>198</v>
+      </c>
+      <c r="E36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
+        <v>0</v>
+      </c>
+      <c r="M36" s="10">
+        <v>0</v>
+      </c>
+      <c r="N36" s="10">
+        <v>0</v>
+      </c>
+      <c r="O36" s="10">
+        <v>0</v>
+      </c>
+      <c r="P36" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>0</v>
+      </c>
+      <c r="R36" s="10">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="11">
+        <f>0+SUBSTITUTE(B36,"s","")</f>
+        <v>0.001</v>
+      </c>
+      <c r="AG36">
+        <f>1-AE36-AF36</f>
+        <v>1</v>
+      </c>
+      <c r="AH36">
+        <f>AE36*$AD36</f>
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <f>AF36*$AD36</f>
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <f>AG36*$AD36</f>
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37">
+        <v>66</v>
+      </c>
+      <c r="E37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37" s="10">
+        <v>0</v>
+      </c>
+      <c r="M37" s="10">
+        <v>0</v>
+      </c>
+      <c r="N37" s="10">
+        <v>0</v>
+      </c>
+      <c r="O37" s="10">
+        <v>0</v>
+      </c>
+      <c r="P37" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>0</v>
+      </c>
+      <c r="R37" s="10">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="11">
+        <f>0+SUBSTITUTE(B37,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <f>1-AE37-AF37</f>
+        <v>1</v>
+      </c>
+      <c r="AH37">
+        <f>AE37*$AD37</f>
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <f>AF37*$AD37</f>
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <f>AG37*$AD37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38">
+        <v>460</v>
+      </c>
+      <c r="E38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0</v>
+      </c>
+      <c r="H38" s="8">
+        <v>0.001</v>
+      </c>
+      <c r="I38" s="8">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="J38" s="10">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>453</v>
+      </c>
+      <c r="L38" s="10">
+        <v>0</v>
+      </c>
+      <c r="M38" s="10">
+        <v>0</v>
+      </c>
+      <c r="N38" s="10">
+        <v>0</v>
+      </c>
+      <c r="O38" s="10">
+        <v>0</v>
+      </c>
+      <c r="P38" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>0</v>
+      </c>
+      <c r="R38" s="10">
+        <v>0</v>
+      </c>
+      <c r="S38" s="9">
+        <v>7302</v>
+      </c>
+      <c r="T38" s="9">
+        <v>6127</v>
+      </c>
+      <c r="U38" s="9">
+        <v>17376</v>
+      </c>
+      <c r="V38" s="9">
+        <v>71300</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>1.9079999999999999</v>
+      </c>
+      <c r="Y38">
+        <v>0.031</v>
+      </c>
+      <c r="Z38">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="AA38">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="AB38">
+        <v>96</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="11">
+        <f>0+SUBSTITUTE(B38,"s","")</f>
+        <v>0.002</v>
+      </c>
+      <c r="AG38">
+        <f>1-AE38-AF38</f>
+        <v>1</v>
+      </c>
+      <c r="AH38">
+        <f>AE38*$AD38</f>
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <f>AF38*$AD38</f>
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <f>AG38*$AD38</f>
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2225</v>
+      </c>
+      <c r="E39" t="s">
+        <v>178</v>
+      </c>
+      <c r="F39">
+        <v>308.608</v>
+      </c>
+      <c r="G39" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="H39" s="8">
+        <v>0.253</v>
+      </c>
+      <c r="I39" s="8">
+        <v>0.43700000000000006</v>
+      </c>
+      <c r="J39" s="8">
+        <v>0.28300000000000003</v>
+      </c>
+      <c r="K39" s="9">
+        <v>3949008</v>
+      </c>
+      <c r="L39" s="10">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="M39" s="10">
+        <v>0</v>
+      </c>
+      <c r="N39" s="8">
+        <v>0.070999999999999994</v>
+      </c>
+      <c r="O39" s="8">
+        <v>0.013999999999999999</v>
+      </c>
+      <c r="P39" s="8">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>0.156</v>
+      </c>
+      <c r="R39" s="10">
+        <v>0</v>
+      </c>
+      <c r="S39" s="9">
+        <v>7440230788</v>
+      </c>
+      <c r="T39" s="9">
+        <v>1482849950</v>
+      </c>
+      <c r="U39" s="9">
+        <v>15250723040</v>
+      </c>
+      <c r="V39" s="9">
+        <v>16489553012</v>
+      </c>
+      <c r="W39" s="9">
+        <v>607131</v>
+      </c>
+      <c r="X39">
+        <v>154.27500000000001</v>
+      </c>
+      <c r="Y39">
+        <v>193.72200000000001</v>
+      </c>
+      <c r="Z39">
+        <v>92.460999999999999</v>
+      </c>
+      <c r="AA39">
+        <v>142.25299999999999</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>80100261</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="11">
+        <f>0+SUBSTITUTE(B39,"s","")</f>
+        <v>0.153</v>
+      </c>
+      <c r="AG39">
+        <f>1-AE39-AF39</f>
+        <v>1</v>
+      </c>
+      <c r="AH39">
+        <f>AE39*$AD39</f>
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <f>AF39*$AD39</f>
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <f>AG39*$AD39</f>
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" s="17">
+        <v>1066.857</v>
+      </c>
+      <c r="G40" s="10">
+        <v>0</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0</v>
+      </c>
+      <c r="I40" s="10">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10">
+        <v>0</v>
+      </c>
+      <c r="N40" s="10">
+        <v>0</v>
+      </c>
+      <c r="O40" s="10">
+        <v>0</v>
+      </c>
+      <c r="P40" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="10">
+        <v>0</v>
+      </c>
+      <c r="R40" s="10">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="11">
+        <f>0+SUBSTITUTE(B40,"s","")</f>
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <f>1-AE40-AF40</f>
+        <v>1</v>
+      </c>
+      <c r="AH40">
+        <f>AE40*$AD40</f>
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <f>AF40*$AD40</f>
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <f>AG40*$AD40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6"/>
+      <c r="AD41" s="18">
+        <f>SUM(AD2:AD40)</f>
+        <v>3.4699999999999984</v>
+      </c>
+      <c r="AE41" s="19"/>
+      <c r="AF41" s="19"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="12">
+        <f>SUM(AH2:AH40)</f>
+        <v>0</v>
+      </c>
+      <c r="AI41" s="12">
+        <f>SUM(AI2:AI40)</f>
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="AJ41" s="12">
+        <f>SUM(AJ2:AJ40)</f>
+        <v>2.8689999999999984</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="AH42" s="14">
+        <f>AH41/$AD$41</f>
+        <v>0</v>
+      </c>
+      <c r="AI42" s="14">
+        <f>AI41/$AD$41</f>
+        <v>0.17319884726224791</v>
+      </c>
+      <c r="AJ42" s="14">
+        <f>AJ41/$AD$41</f>
+        <v>0.82680115273775212</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+  </sheetData>
+  <conditionalFormatting sqref="AD2:AD40">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min" val="&quot;&quot;"/>
+        <cfvo type="max" val="&quot;&quot;"/>
+        <color theme="9" tint="0.79998168889431442"/>
+        <color rgb="FFFAD5D5"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14330,39 +19255,39 @@
   <sheetData>
     <row r="1">
       <c r="H1" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="I1" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="J1" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="K1" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H2">
         <v>9.5999999999999996</v>
@@ -14377,33 +19302,33 @@
         <v>21.16</v>
       </c>
       <c r="L2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>79</v>
+        <v>192</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H3">
         <v>13.41</v>
@@ -14418,31 +19343,31 @@
         <v>20.75</v>
       </c>
       <c r="L3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q3" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="Q3" s="20"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H4">
         <v>13.720000000000001</v>
@@ -14457,7 +19382,7 @@
         <v>22.010000000000002</v>
       </c>
       <c r="L4" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="M4">
         <f>STDEV(H2:H4)/AVERAGE(H2:H4)*100</f>
@@ -14475,29 +19400,29 @@
         <f>STDEV(K2:K4)/AVERAGE(K2:K4)*100</f>
         <v>3.0163174010526634</v>
       </c>
-      <c r="Q4" s="6"/>
+      <c r="Q4" s="20"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H5">
         <v>4.9100000000000001</v>
@@ -14512,31 +19437,31 @@
         <v>6.8499999999999996</v>
       </c>
       <c r="L5" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q5" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="Q5" s="20"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H6">
         <v>5.2199999999999998</v>
@@ -14551,31 +19476,31 @@
         <v>6.8600000000000003</v>
       </c>
       <c r="L6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q6" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="Q6" s="20"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H7">
         <v>5.2000000000000002</v>
@@ -14590,7 +19515,7 @@
         <v>6.8600000000000003</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="M7" s="3">
         <f>STDEV(H5:H7)/AVERAGE(H5:H7)*100</f>
@@ -14608,29 +19533,29 @@
         <f>STDEV(K5:K7)/AVERAGE(K5:K7)*100</f>
         <v>0.084202761670831031</v>
       </c>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="20"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H8">
         <v>6.3600000000000003</v>
@@ -14645,31 +19570,31 @@
         <v>9.3300000000000001</v>
       </c>
       <c r="L8" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="Q8" s="20"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H9">
         <v>6.3799999999999999</v>
@@ -14684,31 +19609,31 @@
         <v>9.3399999999999999</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q9" s="6"/>
+        <v>192</v>
+      </c>
+      <c r="Q9" s="20"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="H10">
         <v>6.1699999999999999</v>
@@ -14723,7 +19648,7 @@
         <v>9.3399999999999999</v>
       </c>
       <c r="L10" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="M10" s="3">
         <f>STDEV(H8:H10)/AVERAGE(H8:H10)*100</f>
@@ -14741,7 +19666,7 @@
         <f>STDEV(K8:K10)/AVERAGE(K8:K10)*100</f>
         <v>0.061836872815738672</v>
       </c>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="20"/>
     </row>
     <row r="11">
       <c r="M11">
@@ -14761,7 +19686,7 @@
         <v>3.0163174010526634</v>
       </c>
       <c r="Q11" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -14782,12 +19707,12 @@
         <v>1.054119011846411</v>
       </c>
       <c r="Q12" t="s">
-        <v>90</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14">
       <c r="M14" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -14804,7 +19729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -14853,7 +19778,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="B4">
         <v>11.9</v>
